--- a/Templates/bulkImport/config/construct_RFI_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_RFI_config_sabah.xlsx
@@ -4,17 +4,33 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="raw_wir" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">raw_wir!$A$4:$BV$4</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="128">
   <si>
     <t>*</t>
   </si>
@@ -22,52 +38,232 @@
     <t>show</t>
   </si>
   <si>
-    <t>c_action_type</t>
+    <t>c_action</t>
   </si>
   <si>
     <t>c_ref_no</t>
   </si>
   <si>
+    <t>c_revision_no</t>
+  </si>
+  <si>
     <t>c_work_discipline</t>
   </si>
   <si>
     <t>c_utility_provider</t>
   </si>
   <si>
+    <t>c_utility_provider_other</t>
+  </si>
+  <si>
+    <t>c_description</t>
+  </si>
+  <si>
     <t>c_propose_date</t>
   </si>
   <si>
     <t>c_propose_time</t>
   </si>
   <si>
-    <t>c_description</t>
+    <t>c_work_permit</t>
+  </si>
+  <si>
+    <t>c_work_permit_thirdParty</t>
   </si>
   <si>
     <t>c_location</t>
   </si>
   <si>
+    <t>c_approved_ms</t>
+  </si>
+  <si>
+    <t>c_approved_inspect_test</t>
+  </si>
+  <si>
+    <t>c_file    </t>
+  </si>
+  <si>
+    <t>c_created_by</t>
+  </si>
+  <si>
+    <t>c_date_created</t>
+  </si>
+  <si>
+    <t>c_time_created</t>
+  </si>
+  <si>
+    <t>c_confirmed_by</t>
+  </si>
+  <si>
+    <t>c_lat</t>
+  </si>
+  <si>
+    <t>c_lon</t>
+  </si>
+  <si>
+    <t>c_actioner</t>
+  </si>
+  <si>
+    <t>c_action_date</t>
+  </si>
+  <si>
+    <t>c_status</t>
+  </si>
+  <si>
+    <t>c_acknowledge</t>
+  </si>
+  <si>
+    <t>c_acknowledge_name</t>
+  </si>
+  <si>
+    <t>c_acknowledge_position</t>
+  </si>
+  <si>
+    <t>c_acknowledge_company</t>
+  </si>
+  <si>
+    <t>c_acknowledge_time</t>
+  </si>
+  <si>
+    <t>c_acknowledge_date</t>
+  </si>
+  <si>
+    <t>c_acknowlegde_file</t>
+  </si>
+  <si>
+    <t>c_acknowledge_remarks</t>
+  </si>
+  <si>
+    <t>c_applicable_review</t>
+  </si>
+  <si>
+    <t>c_wir_approval_sabah</t>
+  </si>
+  <si>
+    <t>c_app_file</t>
+  </si>
+  <si>
+    <t>c_app_remarks</t>
+  </si>
+  <si>
+    <t>c_inspection_type</t>
+  </si>
+  <si>
+    <t>c_remarks</t>
+  </si>
+  <si>
+    <t>c_inspector</t>
+  </si>
+  <si>
+    <t>c_inspector_position</t>
+  </si>
+  <si>
+    <t>c_inspection_date</t>
+  </si>
+  <si>
+    <t>c_inspection_approval</t>
+  </si>
+  <si>
+    <t>c_inspection_approval_reason</t>
+  </si>
+  <si>
+    <t>c_inspection_unapproved_reason</t>
+  </si>
+  <si>
+    <t>c_inspection_remarks</t>
+  </si>
+  <si>
+    <t>c_inspection_app_file</t>
+  </si>
+  <si>
+    <t>c_require_document</t>
+  </si>
+  <si>
     <t>c_date_approved</t>
   </si>
   <si>
-    <t>c_require_document</t>
-  </si>
-  <si>
-    <t>c_file</t>
-  </si>
-  <si>
-    <t>c_actioner</t>
-  </si>
-  <si>
-    <t>c_action</t>
-  </si>
-  <si>
-    <t>c_action_status</t>
+    <t>c_issued_by</t>
+  </si>
+  <si>
+    <t>c_time_issued</t>
+  </si>
+  <si>
+    <t>c_attachment_doc</t>
+  </si>
+  <si>
+    <t>c_doc_submitted_by</t>
+  </si>
+  <si>
+    <t>c_doc_submitted_date</t>
+  </si>
+  <si>
+    <t>c_doc_submitted_time</t>
+  </si>
+  <si>
+    <t>c_wir_doc_status</t>
+  </si>
+  <si>
+    <t>c_close_out_date</t>
+  </si>
+  <si>
+    <t>c_review_doc_file</t>
+  </si>
+  <si>
+    <t>c_review_doc_remarks</t>
+  </si>
+  <si>
+    <t>c_recommendation_act</t>
+  </si>
+  <si>
+    <t>c_recommend_remarks</t>
+  </si>
+  <si>
+    <t>c_recommend_by</t>
+  </si>
+  <si>
+    <t>c_recommend_date</t>
+  </si>
+  <si>
+    <t>c_verify_status</t>
+  </si>
+  <si>
+    <t>c_verify_file</t>
+  </si>
+  <si>
+    <t>c_verify_remarks</t>
+  </si>
+  <si>
+    <t>c_verify_by</t>
+  </si>
+  <si>
+    <t>c_verify_date</t>
+  </si>
+  <si>
+    <t>c_acknowledge_reject</t>
+  </si>
+  <si>
+    <t>c_acknowledge_reject_name</t>
+  </si>
+  <si>
+    <t>c_acknowledge_reject_position</t>
+  </si>
+  <si>
+    <t>c_acknowledge_reject_company</t>
+  </si>
+  <si>
+    <t>c_acknowledge_reject_time</t>
+  </si>
+  <si>
+    <t>c_acknowledge_reject_date</t>
   </si>
   <si>
     <t>Action</t>
   </si>
   <si>
-    <t>RFI Reference No</t>
+    <t>RFI Ref. No.</t>
+  </si>
+  <si>
+    <t>Revision No.</t>
   </si>
   <si>
     <t>Work Discipline</t>
@@ -76,47 +272,169 @@
     <t>Utility Provider</t>
   </si>
   <si>
+    <t>Others (Please Specify)</t>
+  </si>
+  <si>
+    <t>Description of Work</t>
+  </si>
+  <si>
     <t>Date of Inspection</t>
   </si>
   <si>
     <t>Time of Inspection</t>
   </si>
   <si>
-    <t>Description of Work</t>
-  </si>
-  <si>
-    <t>Location of Work</t>
-  </si>
-  <si>
-    <t>Approval Date</t>
-  </si>
-  <si>
-    <t>Approval Status</t>
+    <t>Permit to Work (PTW)</t>
+  </si>
+  <si>
+    <t>Permit to Wor for Third Party</t>
+  </si>
+  <si>
+    <t>Location of Work (CH No. / gridline / structure element/etc.)</t>
+  </si>
+  <si>
+    <t>Method Statement for work has been approved?</t>
+  </si>
+  <si>
+    <t>Inspection &amp; Test Plan for work has been submitted and approved?</t>
   </si>
   <si>
     <t>File</t>
   </si>
   <si>
+    <t>Submitter Name (WPC)</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Confirmed By</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
     <t>Actioner</t>
   </si>
   <si>
+    <t>Action Date</t>
+  </si>
+  <si>
+    <t>Action Status</t>
+  </si>
+  <si>
+    <t>Acknowledge</t>
+  </si>
+  <si>
+    <t>Acknowledger Name</t>
+  </si>
+  <si>
+    <t>Acknowledger Position</t>
+  </si>
+  <si>
+    <t>Acknowledger Company</t>
+  </si>
+  <si>
+    <t>Attachment</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Applicable for RE?</t>
+  </si>
+  <si>
+    <t>RFI Accepted for Inspection?</t>
+  </si>
+  <si>
+    <t>Type of Work Inspection</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Inspection Approval</t>
+  </si>
+  <si>
+    <t>Reasons for Approved Inspection</t>
+  </si>
+  <si>
+    <t>Reasons for Unapproved/Rejected Inspection</t>
+  </si>
+  <si>
+    <t>Remarks (please state reasons)</t>
+  </si>
+  <si>
+    <t>Require Supporting Document?</t>
+  </si>
+  <si>
+    <t>Approved Date</t>
+  </si>
+  <si>
+    <t>Issued By</t>
+  </si>
+  <si>
+    <t>Time Issued</t>
+  </si>
+  <si>
+    <t>Attachment(s)</t>
+  </si>
+  <si>
+    <t>Submitted By</t>
+  </si>
+  <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Close Out Date</t>
+  </si>
+  <si>
+    <t>Recommend?</t>
+  </si>
+  <si>
+    <t>Recommended By</t>
+  </si>
+  <si>
+    <t>Verify?</t>
+  </si>
+  <si>
+    <t>Verified By</t>
+  </si>
+  <si>
+    <t>Acknowledge Reject?</t>
+  </si>
+  <si>
+    <t>Company</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -575,153 +893,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1070,58 +1392,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:BV5"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="13.4444444444444" customWidth="1"/>
-    <col min="2" max="2" width="8.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="19.6666666666667" customWidth="1"/>
-    <col min="4" max="5" width="17.4444444444444" customWidth="1"/>
-    <col min="6" max="6" width="17.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="18.8888888888889" customWidth="1"/>
-    <col min="8" max="11" width="17.6666666666667" customWidth="1"/>
-    <col min="12" max="12" width="15.3333333333333" customWidth="1"/>
-    <col min="13" max="13" width="10.1111111111111" customWidth="1"/>
-    <col min="14" max="14" width="8.11111111111111" customWidth="1"/>
-    <col min="15" max="15" width="21.1111111111111" customWidth="1"/>
-    <col min="16" max="16" width="24.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="22.1111111111111" customWidth="1"/>
-    <col min="18" max="18" width="15.3333333333333" customWidth="1"/>
-    <col min="19" max="19" width="20.8888888888889" customWidth="1"/>
-    <col min="20" max="20" width="24" customWidth="1"/>
-    <col min="21" max="21" width="19.8888888888889" customWidth="1"/>
-    <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="24.3333333333333" customWidth="1"/>
-    <col min="24" max="24" width="23.3333333333333" customWidth="1"/>
-    <col min="25" max="25" width="14.6666666666667" customWidth="1"/>
-    <col min="26" max="26" width="12.6666666666667" customWidth="1"/>
-    <col min="27" max="27" width="11.8888888888889" customWidth="1"/>
-    <col min="28" max="28" width="15.1111111111111" customWidth="1"/>
-    <col min="29" max="29" width="11.1111111111111" customWidth="1"/>
-    <col min="30" max="30" width="16" customWidth="1"/>
-    <col min="31" max="31" width="16.1111111111111" customWidth="1"/>
-    <col min="32" max="32" width="8.88888888888889" customWidth="1"/>
-    <col min="33" max="33" width="10.1111111111111" customWidth="1"/>
-    <col min="34" max="34" width="13.4444444444444" customWidth="1"/>
-    <col min="35" max="35" width="19.6666666666667" customWidth="1"/>
-    <col min="36" max="36" width="12.1111111111111" customWidth="1"/>
-    <col min="37" max="37" width="5.11111111111111" customWidth="1"/>
-    <col min="38" max="38" width="5.66666666666667" customWidth="1"/>
-    <col min="39" max="39" width="19.4444444444444" customWidth="1"/>
-    <col min="40" max="40" width="19.6666666666667" customWidth="1"/>
-    <col min="41" max="41" width="16.3333333333333" customWidth="1"/>
-    <col min="42" max="42" width="11.1111111111111" customWidth="1"/>
-    <col min="43" max="43" width="16.8888888888889" customWidth="1"/>
-    <col min="44" max="44" width="13.1111111111111" customWidth="1"/>
-    <col min="45" max="45" width="22.1111111111111" customWidth="1"/>
-    <col min="46" max="46" width="18.8888888888889" customWidth="1"/>
-    <col min="47" max="47" width="20.8888888888889" customWidth="1"/>
-    <col min="48" max="48" width="21.6666666666667" customWidth="1"/>
-    <col min="49" max="49" width="22.4444444444444" customWidth="1"/>
-    <col min="50" max="50" width="20.6666666666667" customWidth="1"/>
-    <col min="51" max="51" width="24.5555555555556" customWidth="1"/>
-    <col min="52" max="52" width="20.4444444444444" customWidth="1"/>
-    <col min="53" max="53" width="15.8888888888889" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="4.11111111111111" customWidth="1"/>
+    <col min="3" max="3" width="7.55555555555556" customWidth="1"/>
+    <col min="4" max="4" width="13.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.8888888888889" customWidth="1"/>
+    <col min="6" max="6" width="12.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="9" width="9.22222222222222" customWidth="1"/>
+    <col min="10" max="10" width="10.5555555555556" customWidth="1"/>
+    <col min="11" max="11" width="15.2222222222222" customWidth="1"/>
+    <col min="12" max="12" width="7.44444444444444" customWidth="1"/>
+    <col min="13" max="13" width="9.33333333333333" customWidth="1"/>
+    <col min="14" max="14" width="7.88888888888889" customWidth="1"/>
+    <col min="15" max="15" width="3.55555555555556" customWidth="1"/>
+    <col min="16" max="16" width="8.66666666666667" customWidth="1"/>
+    <col min="17" max="17" width="4.66666666666667" customWidth="1"/>
+    <col min="18" max="18" width="4.77777777777778" customWidth="1"/>
+    <col min="19" max="19" width="11.7777777777778" customWidth="1"/>
+    <col min="20" max="20" width="2.77777777777778" customWidth="1"/>
+    <col min="21" max="21" width="3.11111111111111" customWidth="1"/>
+    <col min="22" max="22" width="5" customWidth="1"/>
+    <col min="23" max="23" width="7" customWidth="1"/>
+    <col min="24" max="24" width="10.3333333333333" customWidth="1"/>
+    <col min="25" max="25" width="5" customWidth="1"/>
+    <col min="26" max="27" width="10.5555555555556" customWidth="1"/>
+    <col min="28" max="28" width="12.2222222222222" customWidth="1"/>
+    <col min="29" max="29" width="9.66666666666667" customWidth="1"/>
+    <col min="30" max="30" width="4.77777777777778" customWidth="1"/>
+    <col min="31" max="31" width="4.66666666666667" customWidth="1"/>
+    <col min="32" max="32" width="7.66666666666667" customWidth="1"/>
+    <col min="33" max="33" width="7.77777777777778" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="35" width="14.2222222222222" customWidth="1"/>
+    <col min="36" max="36" width="6.11111111111111" customWidth="1"/>
+    <col min="37" max="37" width="4.44444444444444" customWidth="1"/>
+    <col min="38" max="38" width="5.22222222222222" customWidth="1"/>
+    <col min="39" max="39" width="7" customWidth="1"/>
+    <col min="40" max="40" width="5.66666666666667" customWidth="1"/>
+    <col min="41" max="41" width="7.33333333333333" customWidth="1"/>
+    <col min="42" max="42" width="4.66666666666667" customWidth="1"/>
+    <col min="43" max="43" width="9.22222222222222" customWidth="1"/>
+    <col min="44" max="44" width="10.4444444444444" customWidth="1"/>
+    <col min="45" max="45" width="18.6666666666667" customWidth="1"/>
+    <col min="46" max="46" width="14" customWidth="1"/>
+    <col min="47" max="47" width="10.3333333333333" customWidth="1"/>
+    <col min="48" max="48" width="10.1111111111111" customWidth="1"/>
+    <col min="49" max="49" width="12.8888888888889" customWidth="1"/>
+    <col min="50" max="50" width="8.33333333333333" customWidth="1"/>
+    <col min="51" max="51" width="10.3333333333333" customWidth="1"/>
+    <col min="52" max="52" width="12.2222222222222" customWidth="1"/>
+    <col min="53" max="53" width="11.4444444444444" customWidth="1"/>
+    <col min="54" max="54" width="4.66666666666667" customWidth="1"/>
+    <col min="55" max="55" width="4.77777777777778" customWidth="1"/>
+    <col min="56" max="56" width="5.77777777777778" customWidth="1"/>
+    <col min="57" max="57" width="8.66666666666667" customWidth="1"/>
+    <col min="58" max="58" width="7.66666666666667" customWidth="1"/>
+    <col min="59" max="59" width="7.77777777777778" customWidth="1"/>
+    <col min="60" max="60" width="9" customWidth="1"/>
+    <col min="61" max="61" width="7.77777777777778" customWidth="1"/>
+    <col min="62" max="62" width="8.22222222222222" customWidth="1"/>
+    <col min="63" max="63" width="4.66666666666667" customWidth="1"/>
+    <col min="64" max="64" width="6.44444444444444" customWidth="1"/>
+    <col min="65" max="65" width="8.66666666666667" customWidth="1"/>
+    <col min="66" max="66" width="7.77777777777778" customWidth="1"/>
+    <col min="67" max="67" width="7.11111111111111" customWidth="1"/>
+    <col min="68" max="68" width="4.66666666666667" customWidth="1"/>
+    <col min="69" max="69" width="8.66666666666667" customWidth="1"/>
+    <col min="70" max="70" width="5.66666666666667" customWidth="1"/>
+    <col min="71" max="71" width="7.33333333333333" customWidth="1"/>
+    <col min="72" max="72" width="8.44444444444444" customWidth="1"/>
+    <col min="73" max="73" width="4.77777777777778" customWidth="1"/>
+    <col min="74" max="74" width="4.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1132,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:74">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1175,8 +1520,188 @@
       <c r="N2" t="s">
         <v>1</v>
       </c>
+      <c r="O2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:74">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1219,93 +1744,633 @@
       <c r="N3">
         <v>13</v>
       </c>
+      <c r="O3">
+        <v>14</v>
+      </c>
+      <c r="P3">
+        <v>15</v>
+      </c>
+      <c r="Q3">
+        <v>16</v>
+      </c>
+      <c r="R3">
+        <v>17</v>
+      </c>
+      <c r="S3">
+        <v>18</v>
+      </c>
+      <c r="T3">
+        <v>19</v>
+      </c>
+      <c r="U3">
+        <v>20</v>
+      </c>
+      <c r="V3">
+        <v>21</v>
+      </c>
+      <c r="W3">
+        <v>22</v>
+      </c>
+      <c r="X3">
+        <v>23</v>
+      </c>
+      <c r="Y3">
+        <v>24</v>
+      </c>
+      <c r="Z3">
+        <v>25</v>
+      </c>
+      <c r="AA3">
+        <v>26</v>
+      </c>
+      <c r="AB3">
+        <v>27</v>
+      </c>
+      <c r="AC3">
+        <v>28</v>
+      </c>
+      <c r="AD3">
+        <v>29</v>
+      </c>
+      <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
+        <v>31</v>
+      </c>
+      <c r="AG3">
+        <v>32</v>
+      </c>
+      <c r="AH3">
+        <v>33</v>
+      </c>
+      <c r="AI3">
+        <v>34</v>
+      </c>
+      <c r="AJ3">
+        <v>35</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>37</v>
+      </c>
+      <c r="AM3">
+        <v>38</v>
+      </c>
+      <c r="AN3">
+        <v>39</v>
+      </c>
+      <c r="AO3">
+        <v>40</v>
+      </c>
+      <c r="AP3">
+        <v>41</v>
+      </c>
+      <c r="AQ3">
+        <v>42</v>
+      </c>
+      <c r="AR3">
+        <v>43</v>
+      </c>
+      <c r="AS3">
+        <v>44</v>
+      </c>
+      <c r="AT3">
+        <v>45</v>
+      </c>
+      <c r="AU3">
+        <v>46</v>
+      </c>
+      <c r="AV3">
+        <v>47</v>
+      </c>
+      <c r="AW3">
+        <v>48</v>
+      </c>
+      <c r="AX3">
+        <v>49</v>
+      </c>
+      <c r="AY3">
+        <v>50</v>
+      </c>
+      <c r="AZ3">
+        <v>51</v>
+      </c>
+      <c r="BA3">
+        <v>52</v>
+      </c>
+      <c r="BB3">
+        <v>53</v>
+      </c>
+      <c r="BC3">
+        <v>54</v>
+      </c>
+      <c r="BD3">
+        <v>55</v>
+      </c>
+      <c r="BE3">
+        <v>56</v>
+      </c>
+      <c r="BF3">
+        <v>57</v>
+      </c>
+      <c r="BG3">
+        <v>58</v>
+      </c>
+      <c r="BH3">
+        <v>59</v>
+      </c>
+      <c r="BI3">
+        <v>60</v>
+      </c>
+      <c r="BJ3">
+        <v>61</v>
+      </c>
+      <c r="BK3">
+        <v>62</v>
+      </c>
+      <c r="BL3">
+        <v>63</v>
+      </c>
+      <c r="BM3">
+        <v>64</v>
+      </c>
+      <c r="BN3">
+        <v>65</v>
+      </c>
+      <c r="BO3">
+        <v>66</v>
+      </c>
+      <c r="BP3">
+        <v>67</v>
+      </c>
+      <c r="BQ3">
+        <v>68</v>
+      </c>
+      <c r="BR3">
+        <v>69</v>
+      </c>
+      <c r="BS3">
+        <v>70</v>
+      </c>
+      <c r="BT3">
+        <v>71</v>
+      </c>
+      <c r="BU3">
+        <v>72</v>
+      </c>
+      <c r="BV3">
+        <v>73</v>
+      </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
+    <row r="4" s="1" customFormat="1" ht="100.8" spans="1:74">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N4" t="s">
+      <c r="N4" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="O4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AS4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AU4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AV4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AX4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AY4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AZ4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="BC4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="BD4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="BE4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="BF4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="BG4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="BK4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="BL4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="BM4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="BN4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="BO4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="BP4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="BQ4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="BR4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BS4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="BT4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BU4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BV4" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" t="s">
-        <v>28</v>
+    <row r="5" ht="158.4" spans="1:74">
+      <c r="A5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
